--- a/deploy/mpsv/site_assets/sablona_import_aktivit.xlsx
+++ b/deploy/mpsv/site_assets/sablona_import_aktivit.xlsx
@@ -59,7 +59,7 @@
     <definedName name="P_07_11">Ciselniky!$D$240:$D$241</definedName>
     <definedName name="P_07_12">Ciselniky!$D$242:$D$251</definedName>
     <definedName name="Cis_Procesy">Ciselniky!$C$2:$C$47</definedName>
-    <definedName name="Cis_Utvary">Ciselniky!$H$2:$H$9</definedName>
+    <definedName name="Cis_Utvary">Ciselniky!$H$2:$H$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -194,9 +194,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Aktivity" displayName="Aktivity" ref="A1:I201" headerRowCount="1">
-  <autoFilter ref="A1:I201"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Aktivity" displayName="Aktivity" ref="A1:L201" headerRowCount="1">
+  <autoFilter ref="A1:L201"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Název aktivity (úplný)"/>
     <tableColumn id="2" name="Proces"/>
     <tableColumn id="3" name="Primární dílčí proces (kód)"/>
@@ -206,6 +206,9 @@
     <tableColumn id="7" name="Text pro OŘ"/>
     <tableColumn id="8" name="Sekce"/>
     <tableColumn id="9" name="Stav"/>
+    <tableColumn id="10" name="Vlastník agendy"/>
+    <tableColumn id="11" name="Vlastník procesu"/>
+    <tableColumn id="12" name="Vlastník dílčího procesu"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -500,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -512,6 +515,9 @@
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -558,6 +564,21 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Stav</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Vlastník agendy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Vlastník procesu</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Vlastník dílčího procesu</t>
         </is>
       </c>
     </row>
@@ -589,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -895,6 +916,72 @@
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Nevyplněno = pracovní. 'schváleno' použijte jen u činností, které už prošly schválením.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vlastník agendy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kód útvaru, víc oddělených středníkem; prázdné = nemění se</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Vlastník AGENDY, ne aktivity — kód sekce. Více oddělte '; '. Prázdné = vlastník se nemění. Vyplňujete ho u každého řádku téže agendy, takže musí být všude stejný; jinak import ohlásí rozpor a nic nezapíše.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vlastník procesu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>kód útvaru, víc oddělených středníkem; prázdné = nemění se</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Vlastník PROCESU — kód odboru. Více oddělte '; '. Prázdné = nemění se. Platí totéž o shodě napříč řádky téhož procesu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vlastník dílčího procesu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>kód útvaru, víc oddělených středníkem; prázdné = nemění se</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Vlastník DÍLČÍHO PROCESU — kód odboru. Více oddělte '; '. Prázdné = nemění se. Platí totéž o shodě napříč řádky téhož dílčího procesu.</t>
         </is>
       </c>
     </row>
@@ -997,12 +1084,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Útvar 1 (sekce)</t>
+          <t>Ministr</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1126,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Útvar 3 (sekce)</t>
+          <t>O12</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1168,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Útvar 11 (odbor)</t>
+          <t>O121</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1210,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Útvar 33 (odbor)</t>
+          <t>O122</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1252,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Útvar 111 (oddělení)</t>
+          <t>Sekce 3</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1294,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Útvar 113 (oddělení)</t>
+          <t>O11</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1336,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Útvar 331 (oddělení)</t>
+          <t>O111</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1378,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Útvar 332 (oddělení)</t>
+          <t>O113</t>
         </is>
       </c>
     </row>
@@ -1331,6 +1418,16 @@
           <t>Správa rozpočtu MPSV</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O33</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1363,6 +1460,16 @@
           <t>Správa rozpočtu podřízených organizací MPSV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O331</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1395,6 +1502,16 @@
           <t>Správa rozpočtu ÚP ČR</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O332</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1427,6 +1544,16 @@
           <t>Finanční kontrola podřízených organizací</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sekce 4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1459,6 +1586,16 @@
           <t>Metodické řízení v oblasti programového financování MPSV a resortu.</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O401</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1491,6 +1628,16 @@
           <t>Nastavení a kontrola podmínek realizace akcí a jejich evidence v ISPROFIN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O42</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1523,6 +1670,16 @@
           <t>Finanční řízení jednotlivých akcí.</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O422</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1555,6 +1712,16 @@
           <t>Řízení a koordinace zpracování dokumentací programů kapitoly.</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O424</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1587,6 +1754,16 @@
           <t>Správa programu dotací do sociální oblasti.</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O425</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1619,6 +1796,16 @@
           <t>Zpracování dokumentace programu a řízení realizace akcí ÚP ČR.</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>O44</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1651,6 +1838,16 @@
           <t>Boj proti korupci</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O443</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1683,6 +1880,16 @@
           <t>Oznamování protiprávního jednání</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O445</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1715,6 +1922,16 @@
           <t>Lobbování</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O45</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1747,6 +1964,16 @@
           <t>Tvorba koncepcí a strategií v oblasti výzkumu a vývoje</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>O451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1779,6 +2006,16 @@
           <t>Koordinační a organizační činnosti v oblasti výzkumu a vývoje a odborná podpora</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O452</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1811,6 +2048,16 @@
           <t>Poskytování finanční podpory v oblasti výzkumu a vývoje</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>O453</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1843,6 +2090,16 @@
           <t>Organizace a řízení navazujících nevýzkumných potřeb v další činnosti resortní výzkumné organizace</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sekce 6</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1875,6 +2132,16 @@
           <t>Plánování auditu</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O601</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1907,6 +2174,16 @@
           <t>Výkon auditu</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O32</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1939,6 +2216,16 @@
           <t>Reporting auditu</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O322</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1971,6 +2258,16 @@
           <t>Plánování kontrol</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O323</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2003,6 +2300,16 @@
           <t>Výkon finanční kontroly</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O325</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2035,6 +2342,16 @@
           <t>Výkon kontroly státní správy</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O34</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2067,6 +2384,16 @@
           <t>Výkon ostatních kontrol</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O341</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2099,6 +2426,16 @@
           <t>Výkon státní správy v oblasti kontrol</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O342</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2131,6 +2468,16 @@
           <t>Reporting kontrol</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O35</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2163,6 +2510,16 @@
           <t>Tvorba koncepce a metodiky systému rizik MPSV</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O351</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2195,6 +2552,16 @@
           <t>Metodické řízení v oblasti řídících a kontrolních mechanismů</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O356</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2227,6 +2594,16 @@
           <t>Koordinace, správa a vedení systému řízení rizik</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O357</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2259,6 +2636,16 @@
           <t>Realizace krizového řízení resortu práce a sociálních věcí</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O61</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2291,6 +2678,16 @@
           <t>Zajištění ochrany utajovaných informací</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O611</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2323,6 +2720,16 @@
           <t>Zajištění BOZP a PO MPSV</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2355,6 +2762,16 @@
           <t>Zajištění ochrany a ostrahy objektu MPSV</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O62</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2387,6 +2804,16 @@
           <t>Tvorba koncepce v oblasti sociální politiky včetně reformy veřejných financí</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O621</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2419,6 +2846,16 @@
           <t>Tvorba právních předpisů v oblasti sociální politiky</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O622</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2449,6 +2886,16 @@
       <c r="F45" t="inlineStr">
         <is>
           <t>Metodické řízení a koordinace v oblasti sociální politiky</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O623</t>
         </is>
       </c>
     </row>

--- a/deploy/mpsv/site_assets/sablona_import_aktivit.xlsx
+++ b/deploy/mpsv/site_assets/sablona_import_aktivit.xlsx
@@ -583,18 +583,30 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="8">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=Cis_Procesy</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=INDIRECT("P_"&amp;SUBSTITUTE(LEFT($B2,5),"-","_"))</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>=Cis_Utvary</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
       <formula1>"pracovní,schváleno"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyberte jednu z nabízených hodnot, nebo nechte prázdné." type="list">
+      <formula1>=Cis_Utvary</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -827,7 +839,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Útvary, které se na činnosti podílejí. Více útvarů oddělte '; '.</t>
+          <t>Útvary, které se na činnosti podílejí. Více oddělte '; '. Na rozdíl od sloupce vlevo tu smí být i volný popis ('věcně příslušné útvary', 'podřízené služební úřady') — import tenhle sloupec proti číselníku nekontroluje.</t>
         </is>
       </c>
     </row>
